--- a/app_kit/tests/TESTS_ROOT/xlsx_for_testing/TaxonProfiles/valid_partial_update/Taxon profiles.xlsx
+++ b/app_kit/tests/TESTS_ROOT/xlsx_for_testing/TaxonProfiles/valid_partial_update/Taxon profiles.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Taxon Profiles" sheetId="1" state="visible" r:id="rId3"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="46">
   <si>
     <t xml:space="preserve">Scientific Name</t>
   </si>
@@ -88,30 +88,6 @@
   </si>
   <si>
     <t xml:space="preserve">Primary image (optional)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leaf.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Art Vandeley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CC BY-SA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://imageworld.com/lacerta-agilis.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leaf title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leaf caption</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leaf alt text</t>
   </si>
   <si>
     <t xml:space="preserve">URL</t>
@@ -441,37 +417,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -3766,30 +3742,14 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>29</v>
-      </c>
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
       <c r="I2" s="8"/>
     </row>
   </sheetData>
@@ -3819,19 +3779,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D1" s="13" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>19</v>
@@ -3848,31 +3808,31 @@
         <v>6</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E2" s="8"/>
       <c r="F2" s="8" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E3" s="8"/>
       <c r="F3" s="8"/>
@@ -3880,13 +3840,13 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
@@ -3895,13 +3855,13 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
@@ -3910,13 +3870,13 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
@@ -3925,13 +3885,13 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>

--- a/app_kit/tests/TESTS_ROOT/xlsx_for_testing/TaxonProfiles/valid_partial_update/Taxon profiles.xlsx
+++ b/app_kit/tests/TESTS_ROOT/xlsx_for_testing/TaxonProfiles/valid_partial_update/Taxon profiles.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Taxon Profiles" sheetId="1" state="visible" r:id="rId3"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="47">
   <si>
     <t xml:space="preserve">Scientific Name</t>
   </si>
@@ -34,6 +34,9 @@
   </si>
   <si>
     <t xml:space="preserve">Morphotype (optional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Object class (optional)</t>
   </si>
   <si>
     <t xml:space="preserve">external_media</t>
@@ -520,14 +523,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:ALX27"/>
+  <dimension ref="A1:ALY27"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="33.94"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="38.39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="47.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="47.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="62.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="47.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="47.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="62.6"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -543,11 +546,13 @@
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4"/>
-      <c r="F1" s="5" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="5"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="5" t="s">
+        <v>5</v>
+      </c>
       <c r="H1" s="5"/>
       <c r="I1" s="5"/>
       <c r="J1" s="5"/>
@@ -1553,19 +1558,20 @@
       <c r="ALV1" s="5"/>
       <c r="ALW1" s="5"/>
       <c r="ALX1" s="5"/>
+      <c r="ALY1" s="5"/>
     </row>
     <row r="2" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
-      <c r="E2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="5" t="s">
+      <c r="E2" s="3"/>
+      <c r="F2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="5"/>
+      <c r="G2" s="5" t="s">
+        <v>7</v>
+      </c>
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
       <c r="J2" s="5"/>
@@ -2571,14 +2577,15 @@
       <c r="ALV2" s="5"/>
       <c r="ALW2" s="5"/>
       <c r="ALX2" s="5"/>
+      <c r="ALY2" s="5"/>
     </row>
     <row r="3" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="5"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="4"/>
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
@@ -3585,103 +3592,106 @@
       <c r="ALV3" s="5"/>
       <c r="ALW3" s="5"/>
       <c r="ALX3" s="5"/>
+      <c r="ALY3" s="5"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" s="6"/>
-      <c r="E4" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="8" t="s">
+      <c r="E4" s="6"/>
+      <c r="F4" s="7" t="s">
         <v>10</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="191.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="6"/>
-      <c r="E5" s="9" t="s">
-        <v>12</v>
+      <c r="E5" s="6"/>
+      <c r="F5" s="9" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
     </row>
     <row r="18" customFormat="false" ht="112.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
-      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3714,31 +3724,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3779,60 +3789,60 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D1" s="13" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E2" s="8"/>
       <c r="F2" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E3" s="8"/>
       <c r="F3" s="8"/>
@@ -3840,13 +3850,13 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
@@ -3855,13 +3865,13 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
@@ -3870,13 +3880,13 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
@@ -3885,13 +3895,13 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
@@ -3907,8 +3917,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>